--- a/branches/dev/StructureDefinition-mii-pr-molgen-diagnostische-implikation.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-molgen-diagnostische-implikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T19:08:54+00:00</t>
+    <t>2026-09-11T11:03:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
